--- a/Day13/Reklaam_regressioonianaluus.xlsx
+++ b/Day13/Reklaam_regressioonianaluus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsk-my.sharepoint.com/personal/virve_rani_bcs_ee/Documents/Documents/Andmetarkus/Day4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsk-my.sharepoint.com/personal/virve_rani_bcs_ee/Documents/Documents/andmetarkus_2026_kevad/Day13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{5073DDA3-9A3D-44E6-A9ED-B6F351EC1468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5871D24-C719-41C4-9639-6A3A0F04478B}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{5073DDA3-9A3D-44E6-A9ED-B6F351EC1468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7824FFB0-D6E2-414F-8CE1-AA8933575FCB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A30ADEB3-073F-4D30-A5CE-2B85D2BA5119}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A30ADEB3-073F-4D30-A5CE-2B85D2BA5119}"/>
   </bookViews>
   <sheets>
     <sheet name="Andmestik" sheetId="1" r:id="rId1"/>
@@ -178,9 +178,6 @@
     <t>Normal Probability Plot - sõltuva tunnuse väärtuste ja empiiriliste kvantiilide punktdiagramm - kui sõltuv tunnus on normaaljaotusega, peaksid punktid sellel diagrammil paiknema diagonaalsel sirgel.</t>
   </si>
   <si>
-    <t xml:space="preserve">Korrelatsioonikordaja - näitab, kui tugev on seos (vahemikus -1…1): 0,98 näitab väga tugevat positiivset seost. </t>
-  </si>
-  <si>
     <t>Line Fit Plots funktsioon- ja argumenttunnuse hajuvusdiagrammi, kuhu on täiendava andmeseeriana kantud prognoositud väärtused.</t>
   </si>
   <si>
@@ -221,6 +218,9 @@
   </si>
   <si>
     <t>Residual Plots - prognoosijääkide ja seletava tunnuse hajuvusdiagramm - kui regressioonivõrrand on sobiv, peaksid punktid sellel graafikul paiknema juhuslikult, ühtlaselt hajutatud punktiparvena.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitmene korrelatsioonikordaja - näitab, kui tugev on seos (vahemikus 0…1): 0,98 näitab väga tugevat positiivset seost. </t>
   </si>
 </sst>
 </file>
@@ -5262,13 +5262,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>6865.4948529411768</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3">
         <v>62311.370294117645</v>
@@ -5290,13 +5290,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>6794.2800000000007</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>61814.554999999993</v>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6" t="e">
         <v>#N/A</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="e">
         <v>#N/A</v>
@@ -5318,13 +5318,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7">
         <v>908.78673769504258</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>4522.8160075250998</v>
@@ -5332,13 +5332,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8">
         <v>825893.33461039816</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>20455864.637925286</v>
@@ -5346,13 +5346,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9">
         <v>-0.55219939569650034</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>-0.45844665894440295</v>
@@ -5360,13 +5360,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10">
         <v>2.8613318889023853E-2</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10">
         <v>8.2415010073823985E-2</v>
@@ -5374,13 +5374,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11">
         <v>3811.9500000000007</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11">
         <v>19137.07</v>
@@ -5388,13 +5388,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12">
         <v>5040.33</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>53016.12</v>
@@ -5402,13 +5402,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13">
         <v>8852.2800000000007</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13">
         <v>72153.19</v>
@@ -5416,13 +5416,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B14">
         <v>466853.65</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14">
         <v>4237173.18</v>
@@ -5430,13 +5430,13 @@
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" s="1">
         <v>68</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1">
         <v>68</v>
@@ -5487,7 +5487,7 @@
         <v>0.97634906047845771</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -5721,7 +5721,7 @@
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="N24" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -6044,7 +6044,7 @@
         <v>58683.78</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
